--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
     <sheet name="Специф." sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="ВОР 6с" sheetId="4" r:id="rId3"/>
+    <sheet name="спец 6с" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -142,6 +148,54 @@
   </si>
   <si>
     <t>2.4</t>
+  </si>
+  <si>
+    <t>2.048</t>
+  </si>
+  <si>
+    <t>2.049</t>
+  </si>
+  <si>
+    <t>2.050</t>
+  </si>
+  <si>
+    <t>2.051</t>
+  </si>
+  <si>
+    <t>2.052</t>
+  </si>
+  <si>
+    <t>2.053</t>
+  </si>
+  <si>
+    <t>2.055</t>
+  </si>
+  <si>
+    <t>2.054-2.069</t>
+  </si>
+  <si>
+    <t>Оклейка швов сопряжения бетонных и других поверхностей стен, перегородок (газобетон, ПГП, панели АКОТЕК и др.) стеклохолстом</t>
+  </si>
+  <si>
+    <t>Лента армирующая ( серпянка)_/150мм</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>3.4</t>
   </si>
 </sst>
 </file>
@@ -195,7 +249,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -461,12 +515,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -609,6 +696,18 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -627,14 +726,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -646,6 +757,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -694,7 +808,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -729,7 +843,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1028,13 +1142,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="49" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="50" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="13">
@@ -1120,7 +1234,7 @@
       <c r="A11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="51" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -1250,22 +1364,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="50"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -1450,9 +1564,585 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="64">
+        <v>1</v>
+      </c>
+      <c r="E3" s="63">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="64">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="63">
+        <f>D4*E3</f>
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="64">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="63">
+        <f>D5*E3</f>
+        <v>256.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="42">
+        <v>1</v>
+      </c>
+      <c r="E6" s="43">
+        <f>'спец 6с'!C13</f>
+        <v>333.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>83.454999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8:E9" si="0">$E$6*D8</f>
+        <v>350.51100000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f t="shared" si="0"/>
+        <v>333.82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'спец 6с'!D13</f>
+        <v>502.91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11</f>
+        <v>502.91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>75.436499999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>528.05550000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>97.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
+        <v>836.73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
+        <v>125.5095</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
+        <v>1506.114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>24.01</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="26"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="10">
+        <v>41.24</v>
+      </c>
+      <c r="D5" s="10">
+        <v>153.84</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>195.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="10">
+        <v>153.37</v>
+      </c>
+      <c r="D6" s="10">
+        <v>103.52</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E11" si="0">C6+D6</f>
+        <v>256.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="26">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="10">
+        <v>40.340000000000003</v>
+      </c>
+      <c r="D7" s="10">
+        <v>48.01</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>88.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="10">
+        <v>15.91</v>
+      </c>
+      <c r="D8" s="10">
+        <v>70.86</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>86.77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="D9" s="10">
+        <v>29.57</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="0"/>
+        <v>32.770000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>35.28</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="0"/>
+        <v>35.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="10">
+        <v>43.07</v>
+      </c>
+      <c r="D11" s="10">
+        <v>48.19</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="0"/>
+        <v>91.259999999999991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="10">
+        <v>36.69</v>
+      </c>
+      <c r="D12" s="10">
+        <v>13.64</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" ref="E12" si="1">C12+D12</f>
+        <v>50.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="10">
+        <f>SUM(C5:C12)</f>
+        <v>333.82</v>
+      </c>
+      <c r="D13" s="10">
+        <f>SUM(D5:D12)</f>
+        <v>502.91</v>
+      </c>
+      <c r="E13" s="10">
+        <f>SUM(E5:E12)</f>
+        <v>836.73</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -708,6 +708,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -726,25 +744,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1364,22 +1364,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="60"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="57"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -1601,54 +1601,54 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="64">
+      <c r="D3" s="57">
         <v>1</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="56">
         <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="64">
+      <c r="D4" s="57">
         <v>0.1</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="56">
         <f>D4*E3</f>
         <v>23.3</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="64">
+      <c r="D5" s="57">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="56">
         <f>D5*E3</f>
         <v>256.3</v>
       </c>
@@ -1721,8 +1721,8 @@
         <v>1</v>
       </c>
       <c r="E9" s="19">
-        <f t="shared" si="0"/>
-        <v>333.82</v>
+        <f>$E$6*D9*28.57</f>
+        <v>9537.2374</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
@@ -1757,8 +1757,8 @@
         <v>1</v>
       </c>
       <c r="E11" s="12">
-        <f>$E$10*D11</f>
-        <v>502.91</v>
+        <f>$E$10*D11*32.51</f>
+        <v>16349.6041</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1930,22 +1930,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="53" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="10">

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,20 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
     <sheet name="Специф." sheetId="2" r:id="rId2"/>
     <sheet name="ВОР 6с" sheetId="4" r:id="rId3"/>
     <sheet name="спец 6с" sheetId="3" r:id="rId4"/>
+    <sheet name="ВОР 5с" sheetId="5" r:id="rId5"/>
+    <sheet name="спец 5с" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -196,6 +198,15 @@
   </si>
   <si>
     <t>3.4</t>
+  </si>
+  <si>
+    <t>2.045</t>
+  </si>
+  <si>
+    <t>2.046</t>
+  </si>
+  <si>
+    <t>2.047</t>
   </si>
 </sst>
 </file>
@@ -249,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -548,12 +559,90 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -726,6 +815,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -746,6 +841,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1364,22 +1504,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="65"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -1703,7 +1843,7 @@
         <v>1.05</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" ref="E8:E9" si="0">$E$6*D8</f>
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
         <v>350.51100000000002</v>
       </c>
     </row>
@@ -1930,22 +2070,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -2145,4 +2285,497 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="73"/>
+      <c r="B1" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="76"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <v>323.32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*E3</f>
+        <v>32.332000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3</f>
+        <v>355.65200000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="70">
+        <v>1</v>
+      </c>
+      <c r="E6" s="71">
+        <f>'спец 5с'!C8</f>
+        <v>161.16999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>40.292499999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>169.2285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>4604.6268999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'спец 5с'!D8</f>
+        <v>341.46999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>11101.189699999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>51.220499999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>358.54349999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>97.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
+        <v>502.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
+        <v>75.396000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
+        <v>904.75199999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>24.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="59"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="59">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="10">
+        <v>82.77</v>
+      </c>
+      <c r="D5" s="10">
+        <v>145.32</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>228.08999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="59">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="10">
+        <v>71.44</v>
+      </c>
+      <c r="D6" s="10">
+        <v>123.07</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
+        <v>194.51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="59">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="10">
+        <v>6.96</v>
+      </c>
+      <c r="D7" s="10">
+        <v>73.08</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>80.039999999999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="59"/>
+      <c r="B8" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="10">
+        <f>SUM(C5:C7)</f>
+        <v>161.16999999999999</v>
+      </c>
+      <c r="D8" s="10">
+        <f>SUM(D5:D7)</f>
+        <v>341.46999999999997</v>
+      </c>
+      <c r="E8" s="10">
+        <f>SUM(E5:E7)</f>
+        <v>502.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="61">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -821,6 +821,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -841,51 +886,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1192,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -1211,7 +1211,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
         <v>0</v>
       </c>
@@ -1229,259 +1229,312 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
-        <v>1</v>
-      </c>
-      <c r="B3" s="40" t="s">
+      <c r="A3" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="57">
+        <v>1</v>
+      </c>
+      <c r="E3" s="56">
+        <v>267.16000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="57">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="56">
+        <f>D4*E3</f>
+        <v>26.716000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="57">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="56">
+        <f>D5*E3</f>
+        <v>293.87600000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="39">
+        <v>1</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C6" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="42">
-        <v>1</v>
-      </c>
-      <c r="E3" s="43">
+      <c r="D6" s="42">
+        <v>1</v>
+      </c>
+      <c r="E6" s="43">
         <v>410.02</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D7" s="11">
         <v>0.25</v>
       </c>
-      <c r="E4" s="12">
-        <f>$E$3*D4</f>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
         <v>102.505</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B8" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D8" s="11">
         <v>1.05</v>
       </c>
-      <c r="E5" s="12">
-        <f t="shared" ref="E5:E6" si="0">$E$3*D5</f>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8:E9" si="0">$E$6*D8</f>
         <v>430.52100000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="s">
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="19">
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
         <f t="shared" si="0"/>
         <v>410.02</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C10" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="42">
-        <v>1</v>
-      </c>
-      <c r="E7" s="43">
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
         <v>603.16000000000008</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B11" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="11">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12">
-        <f>$E$7*D8</f>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11</f>
         <v>603.16000000000008</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B12" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D12" s="11">
         <v>0.15</v>
       </c>
-      <c r="E9" s="12">
-        <f t="shared" ref="E9:E10" si="1">$E$7*D9</f>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
         <v>90.474000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B13" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D13" s="11">
         <v>1.05</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E13" s="12">
         <f t="shared" si="1"/>
         <v>633.3180000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B14" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="16">
-        <v>1</v>
-      </c>
-      <c r="E11" s="17">
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
         <v>295.41000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="37" t="s">
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="39">
-        <v>1</v>
-      </c>
-      <c r="B15" s="40" t="s">
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C18" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="42">
-        <v>1</v>
-      </c>
-      <c r="E15" s="43">
-        <f>E7+E3</f>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
         <v>1013.1800000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B19" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C19" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D19" s="13">
         <v>0.15</v>
       </c>
-      <c r="E16" s="19">
-        <f>$E$15*D16</f>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
         <v>151.977</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C20" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D20" s="11">
         <v>1.8</v>
       </c>
-      <c r="E17" s="19">
-        <f>$E$15*D17</f>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
         <v>1823.7240000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C21" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D21" s="22">
         <v>0.3</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E21" s="17">
         <v>24.01</v>
       </c>
     </row>
@@ -1504,22 +1557,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="65"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="80"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -2070,22 +2123,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -2300,28 +2353,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73"/>
-      <c r="B1" s="74" t="s">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="76"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="79" t="s">
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="73" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2329,7 +2382,7 @@
       <c r="A3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="65" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -2346,7 +2399,7 @@
       <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="65" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="10" t="s">
@@ -2364,7 +2417,7 @@
       <c r="A5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="74" t="s">
         <v>51</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -2379,19 +2432,19 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="70">
-        <v>1</v>
-      </c>
-      <c r="E6" s="71">
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="64">
         <f>'спец 5с'!C8</f>
         <v>161.16999999999999</v>
       </c>
@@ -2654,22 +2707,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="59"/>

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,15 @@
     <sheet name="спец 6с" sheetId="3" r:id="rId4"/>
     <sheet name="ВОР 5с" sheetId="5" r:id="rId5"/>
     <sheet name="спец 5с" sheetId="6" r:id="rId6"/>
+    <sheet name="ВОР 4с" sheetId="8" r:id="rId7"/>
+    <sheet name="спец 4с" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="69">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -207,6 +209,30 @@
   </si>
   <si>
     <t>2.047</t>
+  </si>
+  <si>
+    <t>2.036</t>
+  </si>
+  <si>
+    <t>2.038</t>
+  </si>
+  <si>
+    <t>2.039</t>
+  </si>
+  <si>
+    <t>2.040</t>
+  </si>
+  <si>
+    <t>2.041</t>
+  </si>
+  <si>
+    <t>2.042</t>
+  </si>
+  <si>
+    <t>2.071</t>
+  </si>
+  <si>
+    <t>2.043</t>
   </si>
 </sst>
 </file>
@@ -642,7 +668,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -865,6 +891,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1557,22 +1589,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -2123,22 +2155,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -2342,6 +2374,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2697,6 +2732,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2707,22 +2745,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="59"/>
@@ -2822,6 +2860,614 @@
       <c r="E8" s="10">
         <f>SUM(E5:E7)</f>
         <v>502.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <v>396.86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*E3</f>
+        <v>39.686000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3</f>
+        <v>436.54600000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="64">
+        <f>'спец 4с'!C14</f>
+        <v>361.91847680879999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>90.479619202199999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>380.01440064924003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>10340.010882427416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'спец 4с'!D14</f>
+        <v>697.45979058729995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>22674.417791993121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>104.61896858809499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>732.33278011666494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <f>15*3.98</f>
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
+        <v>1059.3782673961</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
+        <v>158.90674010941498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
+        <v>1906.8808813129801</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>24.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="76"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="76" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="76"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="76">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="10">
+        <v>27.473938947900002</v>
+      </c>
+      <c r="D5" s="10">
+        <v>100.70855333499999</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>128.1824922829</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="76">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="10">
+        <v>49.624980822800005</v>
+      </c>
+      <c r="D6" s="10">
+        <v>56.0445512175</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
+        <v>105.6695320403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="76">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="10">
+        <v>42.740829176200002</v>
+      </c>
+      <c r="D7" s="10">
+        <v>59.509028052599994</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>102.2498572288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="76">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="10">
+        <v>69.465545464800002</v>
+      </c>
+      <c r="D8" s="10">
+        <v>36.453381392200001</v>
+      </c>
+      <c r="E8" s="10">
+        <f>C8+D8</f>
+        <v>105.918926857</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="76">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="10">
+        <v>70.613545464799998</v>
+      </c>
+      <c r="D9" s="10">
+        <v>36.0466199233</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" ref="E9:E11" si="1">C9+D9</f>
+        <v>106.6601653881</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="10">
+        <v>18.623236932599998</v>
+      </c>
+      <c r="D10" s="10">
+        <v>171.0372205095</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>189.66045744210001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="10">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D11" s="10">
+        <v>13.64</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>50.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="10">
+        <v>31.876399999699998</v>
+      </c>
+      <c r="D12" s="10">
+        <v>105.4742089912</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" ref="E12:E13" si="2">C12+D12</f>
+        <v>137.35060899090001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="10">
+        <v>14.8</v>
+      </c>
+      <c r="D13" s="10">
+        <v>118.54622716599999</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="2"/>
+        <v>133.34622716600001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(C5:C13)</f>
+        <v>361.91847680879999</v>
+      </c>
+      <c r="D14" s="10">
+        <f>SUM(D5:D13)</f>
+        <v>697.45979058729995</v>
+      </c>
+      <c r="E14" s="10">
+        <f>SUM(C14:D14)</f>
+        <v>1059.3782673961</v>
       </c>
     </row>
   </sheetData>

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -3235,7 +3235,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,18 @@
     <sheet name="спец 5с" sheetId="6" r:id="rId6"/>
     <sheet name="ВОР 4с" sheetId="8" r:id="rId7"/>
     <sheet name="спец 4с" sheetId="9" r:id="rId8"/>
+    <sheet name="ВОР 3э1ч" sheetId="10" r:id="rId9"/>
+    <sheet name="Спец7с3э" sheetId="11" r:id="rId10"/>
+    <sheet name="Спец6с3э" sheetId="12" r:id="rId11"/>
+    <sheet name="Спец5с3э" sheetId="13" r:id="rId12"/>
+    <sheet name="Спец4с3э" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="102">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -233,6 +238,105 @@
   </si>
   <si>
     <t>2.043</t>
+  </si>
+  <si>
+    <t>3.050</t>
+  </si>
+  <si>
+    <t>3.051</t>
+  </si>
+  <si>
+    <t>3.054</t>
+  </si>
+  <si>
+    <t>3.058</t>
+  </si>
+  <si>
+    <t>3.061</t>
+  </si>
+  <si>
+    <t>3.062</t>
+  </si>
+  <si>
+    <t>3.053</t>
+  </si>
+  <si>
+    <t>3.059</t>
+  </si>
+  <si>
+    <t>3.049</t>
+  </si>
+  <si>
+    <t>3.060</t>
+  </si>
+  <si>
+    <t>3.005</t>
+  </si>
+  <si>
+    <t>3.065</t>
+  </si>
+  <si>
+    <t>3.046</t>
+  </si>
+  <si>
+    <t>3.043</t>
+  </si>
+  <si>
+    <t>3.039</t>
+  </si>
+  <si>
+    <t>3.041</t>
+  </si>
+  <si>
+    <t>3.044</t>
+  </si>
+  <si>
+    <t>3.045</t>
+  </si>
+  <si>
+    <t>3.038</t>
+  </si>
+  <si>
+    <t>3.040</t>
+  </si>
+  <si>
+    <t>3.042</t>
+  </si>
+  <si>
+    <t>3.037</t>
+  </si>
+  <si>
+    <t>3.036</t>
+  </si>
+  <si>
+    <t>3.027</t>
+  </si>
+  <si>
+    <t>3.028</t>
+  </si>
+  <si>
+    <t>3.030</t>
+  </si>
+  <si>
+    <t>3.066</t>
+  </si>
+  <si>
+    <t>3.031</t>
+  </si>
+  <si>
+    <t>3.057</t>
+  </si>
+  <si>
+    <t>3.055</t>
+  </si>
+  <si>
+    <t>3.064</t>
+  </si>
+  <si>
+    <t>3.033</t>
+  </si>
+  <si>
+    <t>3.032</t>
   </si>
 </sst>
 </file>
@@ -668,7 +772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -891,6 +995,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1576,6 +1686,813 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="78"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="78">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="78">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10">
+        <f>C8+D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="78">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10">
+        <f t="shared" ref="E9:E15" si="1">C9+D9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="78">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="78">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="78">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="78">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="78">
+        <v>10</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="78">
+        <v>11</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="78"/>
+      <c r="B16" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="10">
+        <f>SUM(C5:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" ref="D16:E16" si="2">SUM(D5:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="B5:B15">
+    <sortCondition ref="B5"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="78"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="78">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="78">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10">
+        <f>C8+D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="78">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10">
+        <f t="shared" ref="E9:E14" si="1">C9+D9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="78">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="78">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="78">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="78">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="78">
+        <v>10</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="78"/>
+      <c r="B15" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="10">
+        <f>SUM(C5:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="10">
+        <f>SUM(D5:D14)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <f>SUM(E5:E14)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="B5:B15">
+    <sortCondition ref="B5"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="78"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6" si="0">C6+D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="78"/>
+      <c r="B7" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="10">
+        <f>SUM(C5:C6)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="10">
+        <f>SUM(D5:D6)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <f>SUM(E5:E6)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="B5:B6">
+    <sortCondition ref="B6"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="78"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6" si="0">C6+D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="78">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10">
+        <f>C7+D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="78">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10">
+        <f t="shared" ref="E8:E12" si="1">C8+D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="78">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="78">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="78">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="78">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="78">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10">
+        <f t="shared" ref="E13:E14" si="2">C13+D13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="78">
+        <v>10</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="78"/>
+      <c r="B15" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="10">
+        <f>SUM(C5:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="10">
+        <f>SUM(D5:D14)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <f>SUM(E5:E14)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
@@ -1589,22 +2506,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="81"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -2155,22 +3072,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -2745,22 +3662,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="59"/>
@@ -3245,22 +4162,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -3477,4 +4394,357 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="5" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -273,9 +273,6 @@
     <t>3.005</t>
   </si>
   <si>
-    <t>3.065</t>
-  </si>
-  <si>
     <t>3.046</t>
   </si>
   <si>
@@ -337,6 +334,9 @@
   </si>
   <si>
     <t>3.032</t>
+  </si>
+  <si>
+    <t>3.035</t>
   </si>
 </sst>
 </file>
@@ -382,12 +382,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="28">
@@ -772,7 +778,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1008,6 +1014,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1027,6 +1036,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1698,22 +1710,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -1750,11 +1762,15 @@
       <c r="B5" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10">
+      <c r="C5" s="10">
+        <v>4.4658036399999999</v>
+      </c>
+      <c r="D5" s="10">
+        <v>69.887666919999987</v>
+      </c>
+      <c r="E5" s="87">
         <f>C5+D5</f>
-        <v>0</v>
+        <v>74.353470559999991</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1764,11 +1780,15 @@
       <c r="B6" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="10">
+        <v>11.899999999999999</v>
+      </c>
+      <c r="D6" s="10">
+        <v>83.583314279999996</v>
+      </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6:E7" si="0">C6+D6</f>
-        <v>0</v>
+        <v>95.483314280000002</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1778,11 +1798,15 @@
       <c r="B7" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10">
+      <c r="C7" s="10">
+        <v>82.408188199999998</v>
+      </c>
+      <c r="D7" s="10">
+        <v>126.88863340000002</v>
+      </c>
+      <c r="E7" s="87">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>209.29682160000002</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1792,11 +1816,15 @@
       <c r="B8" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10">
+      <c r="C8" s="10">
+        <v>66.421027600000002</v>
+      </c>
+      <c r="D8" s="10">
+        <v>220.50730367</v>
+      </c>
+      <c r="E8" s="87">
         <f>C8+D8</f>
-        <v>0</v>
+        <v>286.92833127</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1806,11 +1834,15 @@
       <c r="B9" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10">
+      <c r="C9" s="10">
+        <v>107.2082332</v>
+      </c>
+      <c r="D9" s="10">
+        <v>120.97256036</v>
+      </c>
+      <c r="E9" s="87">
         <f t="shared" ref="E9:E15" si="1">C9+D9</f>
-        <v>0</v>
+        <v>228.18079355999998</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1820,11 +1852,15 @@
       <c r="B10" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="10">
+        <v>58.46</v>
+      </c>
+      <c r="D10" s="10">
+        <v>80.532918559999999</v>
+      </c>
       <c r="E10" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>138.99291855999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1834,11 +1870,15 @@
       <c r="B11" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10">
+      <c r="C11" s="10">
+        <v>32.572800000000001</v>
+      </c>
+      <c r="D11" s="10">
+        <v>101.40153359999999</v>
+      </c>
+      <c r="E11" s="87">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>133.97433359999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1848,11 +1888,15 @@
       <c r="B12" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10">
+      <c r="C12" s="10">
+        <v>12.385599999999998</v>
+      </c>
+      <c r="D12" s="10">
+        <v>16.096</v>
+      </c>
+      <c r="E12" s="87">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>28.4816</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1862,11 +1906,15 @@
       <c r="B13" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10">
+      <c r="C13" s="10">
+        <v>66.115608219999999</v>
+      </c>
+      <c r="D13" s="10">
+        <v>36.970356110000004</v>
+      </c>
+      <c r="E13" s="87">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>103.08596433</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1876,11 +1924,15 @@
       <c r="B14" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10">
+      <c r="C14" s="10">
+        <v>6.8</v>
+      </c>
+      <c r="D14" s="10">
+        <v>47.174515600000007</v>
+      </c>
+      <c r="E14" s="87">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>53.974515600000004</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1890,11 +1942,15 @@
       <c r="B15" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10">
+      <c r="C15" s="10">
+        <v>13.792</v>
+      </c>
+      <c r="D15" s="10">
+        <v>36.183082400000004</v>
+      </c>
+      <c r="E15" s="87">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>49.975082400000005</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1904,15 +1960,15 @@
       </c>
       <c r="C16" s="10">
         <f>SUM(C5:C15)</f>
-        <v>0</v>
+        <v>462.52926085999997</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" ref="D16:E16" si="2">SUM(D5:D15)</f>
-        <v>0</v>
+        <v>940.19788490000008</v>
       </c>
       <c r="E16" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1402.7271457599998</v>
       </c>
     </row>
   </sheetData>
@@ -1929,7 +1985,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -1939,22 +1995,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -1989,13 +2045,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+        <v>86</v>
+      </c>
+      <c r="C5" s="10">
+        <v>62.963999999999999</v>
+      </c>
+      <c r="D5" s="10">
+        <v>181.70322495999997</v>
+      </c>
       <c r="E5" s="10">
         <f>C5+D5</f>
-        <v>0</v>
+        <v>244.66722495999997</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2003,13 +2063,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+        <v>82</v>
+      </c>
+      <c r="C6" s="10">
+        <v>4.3300179999999999</v>
+      </c>
+      <c r="D6" s="10">
+        <v>67.694470760000002</v>
+      </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6:E7" si="0">C6+D6</f>
-        <v>0</v>
+        <v>72.024488759999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2017,13 +2081,17 @@
         <v>3</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+        <v>87</v>
+      </c>
+      <c r="C7" s="10">
+        <v>64.902808519999994</v>
+      </c>
+      <c r="D7" s="10">
+        <v>100.62324375999999</v>
+      </c>
       <c r="E7" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>165.52605227999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2031,13 +2099,17 @@
         <v>4</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+        <v>83</v>
+      </c>
+      <c r="C8" s="10">
+        <v>197.50406935999999</v>
+      </c>
+      <c r="D8" s="10">
+        <v>149.17202871999996</v>
+      </c>
       <c r="E8" s="10">
         <f>C8+D8</f>
-        <v>0</v>
+        <v>346.67609807999997</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2045,13 +2117,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+        <v>88</v>
+      </c>
+      <c r="C9" s="10">
+        <v>16.28</v>
+      </c>
+      <c r="D9" s="10">
+        <v>71.948570680000003</v>
+      </c>
       <c r="E9" s="10">
-        <f t="shared" ref="E9:E14" si="1">C9+D9</f>
-        <v>0</v>
+        <f t="shared" ref="E9:E13" si="1">C9+D9</f>
+        <v>88.228570680000004</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,13 +2135,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="C10" s="10">
+        <v>45.676007200000001</v>
+      </c>
+      <c r="D10" s="10">
+        <v>49.025836000000005</v>
+      </c>
       <c r="E10" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>94.701843200000013</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2073,13 +2153,17 @@
         <v>7</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+        <v>84</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="D11" s="10">
+        <v>29.332000000000001</v>
+      </c>
       <c r="E11" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>32.532000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2087,13 +2171,17 @@
         <v>8</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>35.037599999999998</v>
+      </c>
       <c r="E12" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>35.037599999999998</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,45 +2189,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+        <v>80</v>
+      </c>
+      <c r="C13" s="10">
+        <v>25.695999999999998</v>
+      </c>
+      <c r="D13" s="10">
+        <v>18.758199999999999</v>
+      </c>
       <c r="E13" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44.4542</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="78">
-        <v>10</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="A14" s="78"/>
+      <c r="B14" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(C5:C13)</f>
+        <v>420.55290307999996</v>
+      </c>
+      <c r="D14" s="10">
+        <f>SUM(D5:D13)</f>
+        <v>703.29517487999999</v>
+      </c>
       <c r="E14" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
-      <c r="B15" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="10">
-        <f>SUM(C5:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="10">
-        <f>SUM(D5:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
-        <f>SUM(E5:E14)</f>
-        <v>0</v>
+        <f>SUM(E5:E13)</f>
+        <v>1123.8480779599997</v>
       </c>
     </row>
   </sheetData>
@@ -2166,22 +2244,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -2216,13 +2294,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="C5" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="D5" s="10">
+        <v>98.868097649999996</v>
+      </c>
       <c r="E5" s="10">
         <f>C5+D5</f>
-        <v>0</v>
+        <v>118.06809765</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2230,13 +2312,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C6" s="10">
+        <v>87.732303720000004</v>
+      </c>
+      <c r="D6" s="10">
+        <v>161.63025861</v>
+      </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6" si="0">C6+D6</f>
-        <v>0</v>
+        <v>249.36256233</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2246,15 +2332,15 @@
       </c>
       <c r="C7" s="10">
         <f>SUM(C5:C6)</f>
-        <v>0</v>
+        <v>106.93230372000001</v>
       </c>
       <c r="D7" s="10">
         <f>SUM(D5:D6)</f>
-        <v>0</v>
+        <v>260.49835625999998</v>
       </c>
       <c r="E7" s="10">
         <f>SUM(E5:E6)</f>
-        <v>0</v>
+        <v>367.43065997999997</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -2281,22 +2367,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -2331,13 +2417,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C5" s="10">
+        <v>31.24</v>
+      </c>
+      <c r="D5" s="10">
+        <v>108.48</v>
+      </c>
       <c r="E5" s="10">
         <f>C5+D5</f>
-        <v>0</v>
+        <v>139.72</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,13 +2435,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="C6" s="10">
+        <v>21.409132</v>
+      </c>
+      <c r="D6" s="10">
+        <v>85.789200000000008</v>
+      </c>
       <c r="E6" s="10">
         <f t="shared" ref="E6" si="0">C6+D6</f>
-        <v>0</v>
+        <v>107.19833200000001</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2359,13 +2453,17 @@
         <v>3</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+        <v>93</v>
+      </c>
+      <c r="C7" s="10">
+        <v>47.185615720000008</v>
+      </c>
+      <c r="D7" s="10">
+        <v>70.117447959999993</v>
+      </c>
       <c r="E7" s="10">
         <f>C7+D7</f>
-        <v>0</v>
+        <v>117.30306368000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,13 +2471,17 @@
         <v>4</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+        <v>94</v>
+      </c>
+      <c r="C8" s="10">
+        <v>66.699999999999989</v>
+      </c>
+      <c r="D8" s="10">
+        <v>262.95395388000003</v>
+      </c>
       <c r="E8" s="10">
-        <f t="shared" ref="E8:E12" si="1">C8+D8</f>
-        <v>0</v>
+        <f t="shared" ref="E8:E13" si="1">C8+D8</f>
+        <v>329.65395388000002</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2387,13 +2489,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+        <v>95</v>
+      </c>
+      <c r="C9" s="10">
+        <v>74.399999999999991</v>
+      </c>
+      <c r="D9" s="10">
+        <v>36.715817960000003</v>
+      </c>
       <c r="E9" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>111.11581795999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2401,13 +2507,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+        <v>96</v>
+      </c>
+      <c r="C10" s="10">
+        <v>7.82</v>
+      </c>
+      <c r="D10" s="10">
+        <v>31.377599999999997</v>
+      </c>
       <c r="E10" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39.197599999999994</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2415,13 +2525,17 @@
         <v>7</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+        <v>97</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.2003268</v>
+      </c>
+      <c r="D11" s="10">
+        <v>60.312200000000004</v>
+      </c>
       <c r="E11" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>61.512526800000003</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2429,59 +2543,89 @@
         <v>8</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>63.162099999999995</v>
+      </c>
       <c r="E12" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>63.162099999999995</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="78">
+      <c r="A13" s="79">
         <v>9</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+        <v>99</v>
+      </c>
+      <c r="C13" s="10">
+        <v>25.72</v>
+      </c>
+      <c r="D13" s="10">
+        <v>17.779999999999998</v>
+      </c>
       <c r="E13" s="10">
-        <f t="shared" ref="E13:E14" si="2">C13+D13</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>43.5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="78">
+      <c r="A14" s="79">
         <v>10</v>
       </c>
       <c r="B14" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="10">
+        <v>48.6</v>
+      </c>
+      <c r="D14" s="10">
+        <v>67.62636148</v>
+      </c>
       <c r="E14" s="10">
+        <f t="shared" ref="E14:E15" si="2">C14+D14</f>
+        <v>116.22636148000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="79">
+        <v>11</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="10">
+        <v>75.45</v>
+      </c>
+      <c r="D15" s="10">
+        <v>39.495817960000004</v>
+      </c>
+      <c r="E15" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
-      <c r="B15" s="53" t="s">
+        <v>114.94581796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="78"/>
+      <c r="B16" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="10">
-        <f>SUM(C5:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="10">
-        <f>SUM(D5:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
-        <f>SUM(E5:E14)</f>
-        <v>0</v>
+      <c r="C16" s="10">
+        <f>SUM(C5:C15)</f>
+        <v>399.72507451999996</v>
+      </c>
+      <c r="D16" s="10">
+        <f>SUM(D5:D15)</f>
+        <v>843.81049924000001</v>
+      </c>
+      <c r="E16" s="10">
+        <f>SUM(E5:E15)</f>
+        <v>1243.5355737599998</v>
       </c>
     </row>
   </sheetData>
@@ -2506,22 +2650,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="81"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="82"/>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="25"/>
@@ -3072,22 +3216,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -3662,22 +3806,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="59"/>
@@ -4162,22 +4306,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -4448,7 +4592,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="12">
-        <v>0</v>
+        <f>290*3.8</f>
+        <v>1102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,7 +4611,7 @@
       </c>
       <c r="E4" s="12">
         <f>D4*E3</f>
-        <v>0</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4484,7 +4629,7 @@
       </c>
       <c r="E5" s="17">
         <f>D5*E3</f>
-        <v>0</v>
+        <v>1212.2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
@@ -4501,7 +4646,8 @@
         <v>1</v>
       </c>
       <c r="E6" s="64">
-        <v>0</v>
+        <f>Спец7с3э!C16+Спец6с3э!C14+Спец5с3э!C7+Спец4с3э!C16</f>
+        <v>1389.7395421799999</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4519,7 +4665,7 @@
       </c>
       <c r="E7" s="12">
         <f>$E$6*D7</f>
-        <v>0</v>
+        <v>347.43488554499999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4537,7 +4683,7 @@
       </c>
       <c r="E8" s="12">
         <f t="shared" ref="E8" si="0">$E$6*D8</f>
-        <v>0</v>
+        <v>1459.226519289</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4555,7 +4701,7 @@
       </c>
       <c r="E9" s="19">
         <f>$E$6*D9*28.57</f>
-        <v>0</v>
+        <v>39704.8587200826</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
@@ -4572,7 +4718,8 @@
         <v>1</v>
       </c>
       <c r="E10" s="43">
-        <v>0</v>
+        <f>Спец7с3э!D16+Спец6с3э!D14+Спец5с3э!D7+Спец4с3э!D16</f>
+        <v>2747.8019152800002</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4590,7 +4737,7 @@
       </c>
       <c r="E11" s="12">
         <f>$E$10*D11*32.51</f>
-        <v>0</v>
+        <v>89331.040265752803</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4608,7 +4755,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
-        <v>0</v>
+        <v>412.17028729200001</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -4626,7 +4773,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2885.1920110440005</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4643,7 +4790,8 @@
         <v>1</v>
       </c>
       <c r="E14" s="17">
-        <v>0</v>
+        <f>235.75*4</f>
+        <v>943</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -4688,7 +4836,7 @@
       </c>
       <c r="E18" s="43">
         <f>E10+E6</f>
-        <v>0</v>
+        <v>4137.5414574599999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -4706,7 +4854,7 @@
       </c>
       <c r="E19" s="19">
         <f>$E$18*D19</f>
-        <v>0</v>
+        <v>620.63121861899992</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -4724,7 +4872,7 @@
       </c>
       <c r="E20" s="19">
         <f>$E$18*D20</f>
-        <v>0</v>
+        <v>7447.5746234280005</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4741,7 +4889,7 @@
         <v>0.3</v>
       </c>
       <c r="E21" s="17">
-        <v>0</v>
+        <v>75.13</v>
       </c>
     </row>
   </sheetData>

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="5" activeTab="12"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="спец 5с" sheetId="6" r:id="rId6"/>
     <sheet name="ВОР 4с" sheetId="8" r:id="rId7"/>
     <sheet name="спец 4с" sheetId="9" r:id="rId8"/>
-    <sheet name="ВОР 3э1ч" sheetId="10" r:id="rId9"/>
+    <sheet name="ВОР ч1э3" sheetId="10" r:id="rId9"/>
     <sheet name="Спец7с3э" sheetId="11" r:id="rId10"/>
     <sheet name="Спец6с3э" sheetId="12" r:id="rId11"/>
     <sheet name="Спец5с3э" sheetId="13" r:id="rId12"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="106">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -337,6 +337,18 @@
   </si>
   <si>
     <t>3.035</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (7 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (6 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (5 секция)</t>
+  </si>
+  <si>
+    <t>Штукатурка стен  и базовая шпаклевка (4 секция)</t>
   </si>
 </sst>
 </file>
@@ -382,18 +394,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="28">
@@ -1038,7 +1044,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1711,7 +1717,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="86"/>
@@ -1786,7 +1792,7 @@
       <c r="D6" s="10">
         <v>83.583314279999996</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="87">
         <f t="shared" ref="E6:E7" si="0">C6+D6</f>
         <v>95.483314280000002</v>
       </c>
@@ -1858,7 +1864,7 @@
       <c r="D10" s="10">
         <v>80.532918559999999</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="87">
         <f t="shared" si="1"/>
         <v>138.99291855999999</v>
       </c>
@@ -1996,7 +2002,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="86"/>
@@ -2245,7 +2251,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="86" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="86"/>
@@ -2377,7 +2383,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="84" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="B2" s="84"/>
       <c r="C2" s="84"/>

--- a/school_2/vor_spartac_2_walls.xlsx
+++ b/school_2/vor_spartac_2_walls.xlsx
@@ -9,37 +9,39 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822" firstSheet="11" activeTab="15"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="822"/>
   </bookViews>
   <sheets>
-    <sheet name="ВОР" sheetId="1" r:id="rId1"/>
-    <sheet name="Специф." sheetId="2" r:id="rId2"/>
-    <sheet name="ВОР 6с" sheetId="4" r:id="rId3"/>
-    <sheet name="спец 6с" sheetId="3" r:id="rId4"/>
-    <sheet name="ВОР 5с" sheetId="5" r:id="rId5"/>
-    <sheet name="спец 5с" sheetId="6" r:id="rId6"/>
-    <sheet name="ВОР 4с" sheetId="8" r:id="rId7"/>
-    <sheet name="спец 4с" sheetId="9" r:id="rId8"/>
-    <sheet name="ВОР ч1э3" sheetId="10" r:id="rId9"/>
-    <sheet name="Спец7с3э" sheetId="11" r:id="rId10"/>
-    <sheet name="Спец6с3э" sheetId="12" r:id="rId11"/>
-    <sheet name="Спец5с3э" sheetId="13" r:id="rId12"/>
-    <sheet name="Спец4с3э" sheetId="14" r:id="rId13"/>
-    <sheet name="Table 1" sheetId="15" r:id="rId14"/>
-    <sheet name="Лист2" sheetId="16" r:id="rId15"/>
-    <sheet name="2вор" sheetId="17" r:id="rId16"/>
-    <sheet name="2пом" sheetId="18" r:id="rId17"/>
-    <sheet name="2расчет" sheetId="21" r:id="rId18"/>
-    <sheet name="3вор" sheetId="19" r:id="rId19"/>
-    <sheet name="3пом" sheetId="20" r:id="rId20"/>
-    <sheet name="3расчет" sheetId="22" r:id="rId21"/>
+    <sheet name="ВедомостьОбщая" sheetId="23" r:id="rId1"/>
+    <sheet name="ВОР" sheetId="1" r:id="rId2"/>
+    <sheet name="Специф." sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="ВОР 6с" sheetId="4" r:id="rId4"/>
+    <sheet name="спец 6с" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="ВОР 5с" sheetId="5" r:id="rId6"/>
+    <sheet name="спец 5с" sheetId="6" state="hidden" r:id="rId7"/>
+    <sheet name="ВОР 4с" sheetId="8" r:id="rId8"/>
+    <sheet name="спец 4с" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="ВОР ч1э3" sheetId="10" r:id="rId10"/>
+    <sheet name="Спец7с3э" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet name="Спец6с3э" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="Спец5с3э" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Спец4с3э" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="Table 1" sheetId="15" r:id="rId15"/>
+    <sheet name="Лист2" sheetId="16" r:id="rId16"/>
+    <sheet name="2вор" sheetId="17" r:id="rId17"/>
+    <sheet name="2пом" sheetId="20" state="hidden" r:id="rId18"/>
+    <sheet name="2расчет" sheetId="21" r:id="rId19"/>
+    <sheet name="3вор1.2с" sheetId="19" r:id="rId20"/>
+    <sheet name="3пом" sheetId="18" state="hidden" r:id="rId21"/>
+    <sheet name="3расчет" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr autoRecover="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="226">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -7217,16 +7219,105 @@
   <si>
     <t>Столбец17</t>
   </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Грунтовка БЕТОН-КОНТАКТ_/</t>
+  </si>
+  <si>
+    <t>Сетка штукатурная_/пластиковая/5*5</t>
+  </si>
+  <si>
+    <t>Штукатурка цементная</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Штукатурка стен цементным, цементно-песчаным раствором с предварительной огрунтовкой / толщ. от 21 до 40 мм / высотой до 4 метров (Штукатурка по ж/б поверхностям)</t>
+  </si>
+  <si>
+    <t>Штукатурка стен цементным, цементно-песчаным раствором с предварительной огрунтовкой / толщ. от 21 до 40 мм / высотой до 4 метров
+(Штукатурка  по газобетонному блоку и ПГП)</t>
+  </si>
+  <si>
+    <t>швы</t>
+  </si>
+  <si>
+    <t>штук жб</t>
+  </si>
+  <si>
+    <t>Штукатурка стен (штук. цементная)</t>
+  </si>
+  <si>
+    <t>2эт</t>
+  </si>
+  <si>
+    <t>3эт</t>
+  </si>
+  <si>
+    <t>общая</t>
+  </si>
+  <si>
+    <t>текущь</t>
+  </si>
+  <si>
+    <t>остаток</t>
+  </si>
+  <si>
+    <t>сумма</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Что осталось</t>
+  </si>
+  <si>
+    <t>Библиотека и спорт зал</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7260,11 +7351,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
@@ -7282,6 +7376,8 @@
       <i/>
       <sz val="15.5"/>
       <name val="ISOCPEUR"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <i/>
@@ -7305,9 +7401,18 @@
       <i/>
       <sz val="11"/>
       <name val="ISOCPEUR"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7320,8 +7425,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -7753,13 +7876,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8076,6 +8212,54 @@
     <xf numFmtId="165" fontId="9" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8096,12 +8280,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -8138,6 +8316,30 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -8734,8 +8936,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A5:P143" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" headerRowCellStyle="Обычный 3" dataCellStyle="Обычный 3">
   <autoFilter ref="A5:P143">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="lessThan" val="3000"/>
+      </customFilters>
+    </filterColumn>
     <filterColumn colId="2">
       <filters>
+        <filter val="-"/>
         <filter val="-  грунтовка  &quot;Бетоноконтакт&quot;;_x000a_-  штукатурка_x000a_цементно-песчаным  раствором М100  (армированная стекловолоконной  или пластиковой  сеткой);_x000a_-  грунтовка  глубокого проникновения_x000a_δ  =  20  мм"/>
       </filters>
     </filterColumn>
@@ -9049,7 +9257,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="B1:T11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="5" width="22.42578125" customWidth="1"/>
+    <col min="13" max="13" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="J1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="L1" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="N1" t="s">
+        <v>218</v>
+      </c>
+      <c r="O1" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>218</v>
+      </c>
+      <c r="R1" t="s">
+        <v>218</v>
+      </c>
+      <c r="S1" t="s">
+        <v>218</v>
+      </c>
+      <c r="T1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B2" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="149" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" s="149" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="149" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="149">
+        <v>7</v>
+      </c>
+      <c r="G2" s="149">
+        <v>6</v>
+      </c>
+      <c r="H2" s="149">
+        <v>5</v>
+      </c>
+      <c r="I2" s="149">
+        <v>4</v>
+      </c>
+      <c r="J2" s="149">
+        <v>3</v>
+      </c>
+      <c r="K2" s="149">
+        <v>2</v>
+      </c>
+      <c r="L2" s="149">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>224</v>
+      </c>
+      <c r="N2">
+        <v>7</v>
+      </c>
+      <c r="O2">
+        <v>6</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2">
+        <v>4</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="155">
+        <v>3617.6</v>
+      </c>
+      <c r="D3" s="151">
+        <f>SUM(F3:L3)</f>
+        <v>1991.3284768087999</v>
+      </c>
+      <c r="E3" s="152">
+        <f>C3-D3</f>
+        <v>1626.2715231912</v>
+      </c>
+      <c r="F3" s="153">
+        <f>ВОР!E6</f>
+        <v>410.02</v>
+      </c>
+      <c r="G3" s="153">
+        <f>'ВОР 6с'!E6</f>
+        <v>333.82</v>
+      </c>
+      <c r="H3" s="153">
+        <f>'ВОР 5с'!E6</f>
+        <v>161.16999999999999</v>
+      </c>
+      <c r="I3" s="153">
+        <f>'ВОР 4с'!E6</f>
+        <v>361.91847680879999</v>
+      </c>
+      <c r="J3" s="149"/>
+      <c r="K3" s="153">
+        <f>'2вор'!E6</f>
+        <v>724.40000000000009</v>
+      </c>
+      <c r="L3" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="M3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="156">
+        <v>4510.8</v>
+      </c>
+      <c r="D4" s="151">
+        <f>SUM(F4:L4)</f>
+        <v>3293.4997905873001</v>
+      </c>
+      <c r="E4" s="152">
+        <f>C4-D4</f>
+        <v>1217.3002094127</v>
+      </c>
+      <c r="F4" s="153">
+        <f>ВОР!E10</f>
+        <v>603.16000000000008</v>
+      </c>
+      <c r="G4" s="153">
+        <f>'ВОР 6с'!E10</f>
+        <v>502.91</v>
+      </c>
+      <c r="H4" s="153">
+        <f>'ВОР 5с'!E10</f>
+        <v>341.46999999999997</v>
+      </c>
+      <c r="I4" s="153">
+        <f>'ВОР 4с'!E10</f>
+        <v>697.45979058729995</v>
+      </c>
+      <c r="J4" s="149"/>
+      <c r="K4" s="153">
+        <f>'2вор'!E10</f>
+        <v>1148.5</v>
+      </c>
+      <c r="L4" s="149" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B5" s="149" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="154">
+        <f>SUM(C3:C4)</f>
+        <v>8128.4</v>
+      </c>
+      <c r="D5" s="154">
+        <f t="shared" ref="D5:E5" si="0">SUM(D3:D4)</f>
+        <v>5284.8282673961003</v>
+      </c>
+      <c r="E5" s="154">
+        <f t="shared" si="0"/>
+        <v>2843.5717326039003</v>
+      </c>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B8" s="149" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="149"/>
+      <c r="D8" s="149"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="149"/>
+      <c r="J8" s="149"/>
+      <c r="K8" s="149"/>
+      <c r="L8" s="149"/>
+    </row>
+    <row r="9" spans="2:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="150">
+        <v>3125.2</v>
+      </c>
+      <c r="D9" s="151">
+        <f>SUM(F9:L9)</f>
+        <v>2042.0395421799999</v>
+      </c>
+      <c r="E9" s="152">
+        <f t="shared" ref="E9:E10" si="1">C9-D9</f>
+        <v>1083.1604578199999</v>
+      </c>
+      <c r="F9" s="153">
+        <f>'ВОР ч1э3'!E6</f>
+        <v>1389.7395421799999</v>
+      </c>
+      <c r="G9" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="H9" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="I9" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="J9" s="149"/>
+      <c r="K9" s="153">
+        <f>'3вор1.2с'!E6</f>
+        <v>652.29999999999995</v>
+      </c>
+      <c r="L9" s="149" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="150">
+        <v>4248.8</v>
+      </c>
+      <c r="D10" s="151">
+        <f>SUM(F10:L10)</f>
+        <v>3610.8019152800002</v>
+      </c>
+      <c r="E10" s="152">
+        <f t="shared" si="1"/>
+        <v>637.99808471999995</v>
+      </c>
+      <c r="F10" s="153">
+        <f>'ВОР ч1э3'!E10</f>
+        <v>2747.8019152800002</v>
+      </c>
+      <c r="G10" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="H10" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="I10" s="149" t="s">
+        <v>223</v>
+      </c>
+      <c r="J10" s="149"/>
+      <c r="K10" s="153">
+        <f>'3вор1.2с'!E10</f>
+        <v>863</v>
+      </c>
+      <c r="L10" s="149" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B11" s="149"/>
+      <c r="C11" s="154">
+        <f>SUM(C9:C10)</f>
+        <v>7374</v>
+      </c>
+      <c r="D11" s="154">
+        <f t="shared" ref="D11" si="2">SUM(D9:D10)</f>
+        <v>5652.8414574600001</v>
+      </c>
+      <c r="E11" s="154">
+        <f t="shared" ref="E11" si="3">SUM(E9:E10)</f>
+        <v>1721.1585425399999</v>
+      </c>
+      <c r="F11" s="149"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -9059,105 +9610,107 @@
     <col min="5" max="5" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="37" t="s">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="45" t="s">
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="73" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+    <row r="3" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="11">
         <v>1</v>
       </c>
-      <c r="E3" s="56">
-        <v>267.16000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="E3" s="12">
+        <f>290*3.8</f>
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="11">
         <v>0.1</v>
       </c>
-      <c r="E4" s="56">
+      <c r="E4" s="12">
         <f>D4*E3</f>
-        <v>26.716000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="17">
         <f>D5*E3</f>
-        <v>293.87600000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+        <v>1212.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="63">
         <v>1</v>
       </c>
-      <c r="B6" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="42">
-        <v>1</v>
-      </c>
-      <c r="E6" s="43">
-        <v>410.02</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>1.1000000000000001</v>
+      <c r="E6" s="64">
+        <f>Спец7с3э!C16+Спец6с3э!C14+Спец5с3э!C7+Спец4с3э!C16</f>
+        <v>1389.7395421799999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>8</v>
@@ -9170,12 +9723,12 @@
       </c>
       <c r="E7" s="12">
         <f>$E$6*D7</f>
-        <v>102.505</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>347.43488554499999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>13</v>
@@ -9187,13 +9740,13 @@
         <v>1.05</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" ref="E8:E9" si="0">$E$6*D8</f>
-        <v>430.52100000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49" t="s">
-        <v>19</v>
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>1459.226519289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>17</v>
@@ -9205,13 +9758,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="19">
-        <f t="shared" si="0"/>
-        <v>410.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+        <f>$E$6*D9*28.57</f>
+        <v>39704.8587200826</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>16</v>
@@ -9223,12 +9776,14 @@
         <v>1</v>
       </c>
       <c r="E10" s="43">
-        <v>603.16000000000008</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <f>Спец7с3э!D16+Спец6с3э!D14+Спец5с3э!D7+Спец4с3э!D16</f>
+        <v>2747.8019152800002</v>
+      </c>
+      <c r="G10" s="124"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>17</v>
@@ -9240,13 +9795,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="12">
-        <f>$E$10*D11</f>
-        <v>603.16000000000008</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <f>$E$10*D11*32.51</f>
+        <v>89331.040265752803</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>10</v>
@@ -9259,12 +9814,12 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
-        <v>90.474000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>412.17028729200001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>13</v>
@@ -9277,12 +9832,12 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>633.3180000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2885.1920110440005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>12</v>
@@ -9294,11 +9849,12 @@
         <v>1</v>
       </c>
       <c r="E14" s="17">
-        <v>295.41000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <f>235.75*4</f>
+        <v>943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="37" t="s">
         <v>39</v>
@@ -9339,7 +9895,7 @@
       </c>
       <c r="E18" s="43">
         <f>E10+E6</f>
-        <v>1013.1800000000001</v>
+        <v>4137.5414574599999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -9357,7 +9913,7 @@
       </c>
       <c r="E19" s="19">
         <f>$E$18*D19</f>
-        <v>151.977</v>
+        <v>620.63121861899992</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -9375,7 +9931,7 @@
       </c>
       <c r="E20" s="19">
         <f>$E$18*D20</f>
-        <v>1823.7240000000002</v>
+        <v>7447.5746234280005</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9392,16 +9948,15 @@
         <v>0.3</v>
       </c>
       <c r="E21" s="17">
-        <v>24.01</v>
+        <v>75.13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9413,22 +9968,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -9672,255 +10227,6 @@
       <c r="E16" s="10">
         <f t="shared" si="2"/>
         <v>1402.7271457599998</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState ref="B5:B15">
-    <sortCondition ref="B5"/>
-  </sortState>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-    </row>
-    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="78" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="78"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="78">
-        <v>1</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="10">
-        <v>62.963999999999999</v>
-      </c>
-      <c r="D5" s="10">
-        <v>181.70322495999997</v>
-      </c>
-      <c r="E5" s="10">
-        <f>C5+D5</f>
-        <v>244.66722495999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="78">
-        <v>2</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="10">
-        <v>4.3300179999999999</v>
-      </c>
-      <c r="D6" s="10">
-        <v>67.694470760000002</v>
-      </c>
-      <c r="E6" s="10">
-        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
-        <v>72.024488759999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="78">
-        <v>3</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="10">
-        <v>64.902808519999994</v>
-      </c>
-      <c r="D7" s="10">
-        <v>100.62324375999999</v>
-      </c>
-      <c r="E7" s="10">
-        <f t="shared" si="0"/>
-        <v>165.52605227999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="78">
-        <v>4</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="10">
-        <v>197.50406935999999</v>
-      </c>
-      <c r="D8" s="10">
-        <v>149.17202871999996</v>
-      </c>
-      <c r="E8" s="10">
-        <f>C8+D8</f>
-        <v>346.67609807999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="78">
-        <v>5</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="10">
-        <v>16.28</v>
-      </c>
-      <c r="D9" s="10">
-        <v>71.948570680000003</v>
-      </c>
-      <c r="E9" s="10">
-        <f t="shared" ref="E9:E13" si="1">C9+D9</f>
-        <v>88.228570680000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="78">
-        <v>6</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="10">
-        <v>45.676007200000001</v>
-      </c>
-      <c r="D10" s="10">
-        <v>49.025836000000005</v>
-      </c>
-      <c r="E10" s="10">
-        <f t="shared" si="1"/>
-        <v>94.701843200000013</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="78">
-        <v>7</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="D11" s="10">
-        <v>29.332000000000001</v>
-      </c>
-      <c r="E11" s="10">
-        <f t="shared" si="1"/>
-        <v>32.532000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="78">
-        <v>8</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10">
-        <v>35.037599999999998</v>
-      </c>
-      <c r="E12" s="10">
-        <f t="shared" si="1"/>
-        <v>35.037599999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="78">
-        <v>9</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="10">
-        <v>25.695999999999998</v>
-      </c>
-      <c r="D13" s="10">
-        <v>18.758199999999999</v>
-      </c>
-      <c r="E13" s="10">
-        <f t="shared" si="1"/>
-        <v>44.4542</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
-      <c r="B14" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="10">
-        <f>SUM(C5:C13)</f>
-        <v>420.55290307999996</v>
-      </c>
-      <c r="D14" s="10">
-        <f>SUM(D5:D13)</f>
-        <v>703.29517487999999</v>
-      </c>
-      <c r="E14" s="10">
-        <f>SUM(E5:E13)</f>
-        <v>1123.8480779599997</v>
       </c>
     </row>
   </sheetData>
@@ -9937,6 +10243,255 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="134" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="78"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="78">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="10">
+        <v>62.963999999999999</v>
+      </c>
+      <c r="D5" s="10">
+        <v>181.70322495999997</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C5+D5</f>
+        <v>244.66722495999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="78">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="10">
+        <v>4.3300179999999999</v>
+      </c>
+      <c r="D6" s="10">
+        <v>67.694470760000002</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E7" si="0">C6+D6</f>
+        <v>72.024488759999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="78">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="10">
+        <v>64.902808519999994</v>
+      </c>
+      <c r="D7" s="10">
+        <v>100.62324375999999</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>165.52605227999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="78">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="10">
+        <v>197.50406935999999</v>
+      </c>
+      <c r="D8" s="10">
+        <v>149.17202871999996</v>
+      </c>
+      <c r="E8" s="10">
+        <f>C8+D8</f>
+        <v>346.67609807999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="78">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="10">
+        <v>16.28</v>
+      </c>
+      <c r="D9" s="10">
+        <v>71.948570680000003</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" ref="E9:E13" si="1">C9+D9</f>
+        <v>88.228570680000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="78">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="10">
+        <v>45.676007200000001</v>
+      </c>
+      <c r="D10" s="10">
+        <v>49.025836000000005</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>94.701843200000013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="78">
+        <v>7</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="D11" s="10">
+        <v>29.332000000000001</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>32.532000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="78">
+        <v>8</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>35.037599999999998</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>35.037599999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="78">
+        <v>9</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="10">
+        <v>25.695999999999998</v>
+      </c>
+      <c r="D13" s="10">
+        <v>18.758199999999999</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>44.4542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="78"/>
+      <c r="B14" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="10">
+        <f>SUM(C5:C13)</f>
+        <v>420.55290307999996</v>
+      </c>
+      <c r="D14" s="10">
+        <f>SUM(D5:D13)</f>
+        <v>703.29517487999999</v>
+      </c>
+      <c r="E14" s="10">
+        <f>SUM(E5:E13)</f>
+        <v>1123.8480779599997</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="B5:B15">
+    <sortCondition ref="B5"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9947,22 +10502,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -10058,7 +10613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10070,22 +10625,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="78"/>
@@ -10340,109 +10895,109 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T143"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="81" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" style="81" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" style="81" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" style="81" customWidth="1"/>
     <col min="4" max="4" width="12" style="81" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="81" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="81" customWidth="1"/>
-    <col min="7" max="7" width="43" style="81" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="81" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="81" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="43" style="81" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="12.140625" style="81" customWidth="1"/>
-    <col min="9" max="9" width="22" style="81" customWidth="1"/>
+    <col min="9" max="9" width="22" style="81" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="81" customWidth="1"/>
-    <col min="11" max="11" width="43.85546875" style="81" customWidth="1"/>
+    <col min="11" max="11" width="43.85546875" style="81" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15.85546875" style="81" customWidth="1"/>
-    <col min="13" max="13" width="22.5703125" style="81" customWidth="1"/>
-    <col min="14" max="14" width="22.28515625" style="81" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" style="81" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" style="81" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="19.28515625" style="81" customWidth="1"/>
     <col min="16" max="16" width="15.42578125" style="81" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="81"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="139" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
     </row>
     <row r="2" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="119" t="s">
+      <c r="C2" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
     </row>
     <row r="3" spans="1:19" s="82" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="122"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="113" t="s">
+      <c r="A3" s="142"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="147" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115" t="s">
+      <c r="D3" s="148"/>
+      <c r="E3" s="135" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="116"/>
-      <c r="G3" s="115" t="s">
+      <c r="F3" s="136"/>
+      <c r="G3" s="135" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="116"/>
-      <c r="I3" s="115" t="s">
+      <c r="H3" s="136"/>
+      <c r="I3" s="135" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="116"/>
-      <c r="K3" s="115" t="s">
+      <c r="J3" s="136"/>
+      <c r="K3" s="135" t="s">
         <v>114</v>
       </c>
-      <c r="L3" s="116"/>
-      <c r="M3" s="115" t="s">
+      <c r="L3" s="136"/>
+      <c r="M3" s="135" t="s">
         <v>115</v>
       </c>
-      <c r="N3" s="116"/>
-      <c r="O3" s="117" t="s">
+      <c r="N3" s="136"/>
+      <c r="O3" s="137" t="s">
         <v>116</v>
       </c>
-      <c r="P3" s="118"/>
+      <c r="P3" s="138"/>
     </row>
     <row r="4" spans="1:19" ht="63" x14ac:dyDescent="0.25">
-      <c r="A4" s="123"/>
-      <c r="B4" s="126"/>
+      <c r="A4" s="143"/>
+      <c r="B4" s="146"/>
       <c r="C4" s="94" t="s">
         <v>117</v>
       </c>
@@ -11168,7 +11723,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="93">
         <v>2011</v>
       </c>
@@ -12598,7 +13153,7 @@
         <v>43.199999999999996</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="105" x14ac:dyDescent="0.25">
       <c r="A39" s="93">
         <v>2034</v>
       </c>
@@ -15350,7 +15905,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="98">
         <v>3009</v>
       </c>
@@ -15650,7 +16205,7 @@
         <v>114.5</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="93">
         <v>3015</v>
       </c>
@@ -15750,7 +16305,7 @@
         <v>116.8</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="93">
         <v>3017</v>
       </c>
@@ -15800,7 +16355,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="93">
         <v>3018</v>
       </c>
@@ -16200,7 +16755,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="93">
         <v>3026</v>
       </c>
@@ -16350,7 +16905,7 @@
         <v>110.1</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="93">
         <v>3029</v>
       </c>
@@ -17000,7 +17555,7 @@
         <v>352.3</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="93">
         <v>3042</v>
       </c>
@@ -17050,7 +17605,7 @@
         <v>86.2</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="93">
         <v>3043</v>
       </c>
@@ -17100,7 +17655,7 @@
         <v>86.7</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="93">
         <v>3044</v>
       </c>
@@ -17150,7 +17705,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="93">
         <v>3045</v>
       </c>
@@ -17650,7 +18205,7 @@
         <v>165.6</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="93">
         <v>3055</v>
       </c>
@@ -17700,7 +18255,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="98">
         <v>3057</v>
       </c>
@@ -18100,7 +18655,7 @@
         <v>173.5</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="93">
         <v>3064</v>
       </c>
@@ -18150,7 +18705,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="93">
         <v>3065</v>
       </c>
@@ -18321,7 +18876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19115,272 +19670,1117 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" style="108" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" style="108" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="108" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="108" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="108" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <f>(E6+E10+E15+E20)*0.45</f>
+        <v>969.07500000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*E3</f>
+        <v>96.907500000000013</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3</f>
+        <v>1065.9825000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="64">
+        <f>'2пом'!C20</f>
+        <v>724.40000000000009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>181.10000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>760.62000000000012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>20696.108000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'2пом'!D20</f>
+        <v>1148.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>37337.735000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>172.27500000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>1205.925</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="19">
+        <f>235.75*4</f>
+        <v>943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="118" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="119" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="121">
+        <v>1</v>
+      </c>
+      <c r="E15" s="120">
+        <f>'2пом'!C32</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="121">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="120">
+        <f>D16*$E$15</f>
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="121">
+        <v>1</v>
+      </c>
+      <c r="E17" s="120">
+        <f t="shared" ref="E17:E18" si="2">D17*$E$15</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="118" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="121">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E18" s="120">
+        <f t="shared" si="2"/>
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="118" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="121">
+        <v>1.3</v>
+      </c>
+      <c r="E19" s="120">
+        <f>D19*$E$15*40</f>
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="119" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="121">
+        <v>1</v>
+      </c>
+      <c r="E20" s="120">
+        <f>'2пом'!D32</f>
+        <v>221.60000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="122" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="121">
+        <v>0.15</v>
+      </c>
+      <c r="E21" s="120">
+        <f>$E$20*D21</f>
+        <v>33.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="118" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="121">
+        <v>1</v>
+      </c>
+      <c r="E22" s="120">
+        <f t="shared" ref="E22:E23" si="3">$E$20*D22</f>
+        <v>221.60000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="118" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="121">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E23" s="120">
+        <f t="shared" si="3"/>
+        <v>243.76000000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="118" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="121">
+        <v>1.3</v>
+      </c>
+      <c r="E24" s="120">
+        <f>$E$20*D24*40</f>
+        <v>11523.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="114"/>
+      <c r="B26" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="116" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="116" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="113">
+        <v>1</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="11">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10">
+        <f>'2пом'!E20</f>
+        <v>1872.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="113">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E29" s="10">
+        <f>D29*E28</f>
+        <v>280.935</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" ref="E30:E31" si="4">D30*E29</f>
+        <v>505.68299999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="4"/>
+        <v>151.70489999999998</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" style="108" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="108" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="108" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="108" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="108" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="107"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="107"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="109">
+        <v>1</v>
+      </c>
+      <c r="B5" s="109">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="C5" s="109">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="D5" s="110">
+        <v>48.5</v>
+      </c>
+      <c r="E5" s="110">
+        <f>C5+D5</f>
+        <v>116.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="109">
+        <v>2</v>
+      </c>
+      <c r="B6" s="109">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="C6" s="109">
+        <v>47.5</v>
+      </c>
+      <c r="D6" s="110">
+        <v>60.400000000000006</v>
+      </c>
+      <c r="E6" s="110">
+        <f t="shared" ref="E6:E19" si="0">C6+D6</f>
+        <v>107.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="109">
+        <v>3</v>
+      </c>
+      <c r="B7" s="109">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="C7" s="109">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="D7" s="110">
+        <v>170.6</v>
+      </c>
+      <c r="E7" s="110">
+        <f t="shared" si="0"/>
+        <v>310.89999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="109">
+        <v>4</v>
+      </c>
+      <c r="B8" s="109">
+        <v>2.004</v>
+      </c>
+      <c r="C8" s="109">
+        <v>38.599999999999994</v>
+      </c>
+      <c r="D8" s="110">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="E8" s="110">
+        <f t="shared" si="0"/>
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="126">
+        <v>5</v>
+      </c>
+      <c r="B9" s="109">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="C9" s="109">
+        <v>19.5</v>
+      </c>
+      <c r="D9" s="110">
+        <v>35.5</v>
+      </c>
+      <c r="E9" s="110">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="126">
+        <v>6</v>
+      </c>
+      <c r="B10" s="125">
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="C10" s="109">
+        <v>22.299999999999997</v>
+      </c>
+      <c r="D10" s="110">
+        <v>134</v>
+      </c>
+      <c r="E10" s="110">
+        <f t="shared" si="0"/>
+        <v>156.30000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="126">
+        <v>7</v>
+      </c>
+      <c r="B11" s="109">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="C11" s="109">
+        <v>30</v>
+      </c>
+      <c r="D11" s="110">
+        <v>10.1</v>
+      </c>
+      <c r="E11" s="110">
+        <f t="shared" si="0"/>
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="126">
+        <v>8</v>
+      </c>
+      <c r="B12" s="109">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="C12" s="109">
+        <v>0</v>
+      </c>
+      <c r="D12" s="110">
+        <v>28</v>
+      </c>
+      <c r="E12" s="110">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="126">
+        <v>9</v>
+      </c>
+      <c r="B13" s="109">
+        <v>2.012</v>
+      </c>
+      <c r="C13" s="109">
+        <v>21.299999999999997</v>
+      </c>
+      <c r="D13" s="110">
+        <v>84.2</v>
+      </c>
+      <c r="E13" s="110">
+        <f t="shared" si="0"/>
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="126">
+        <v>10</v>
+      </c>
+      <c r="B14" s="109">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="C14" s="109">
+        <v>22.8</v>
+      </c>
+      <c r="D14" s="110">
+        <v>85.8</v>
+      </c>
+      <c r="E14" s="110">
+        <f t="shared" si="0"/>
+        <v>108.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="109">
+        <v>11</v>
+      </c>
+      <c r="B15" s="109">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="C15" s="109">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="D15" s="110">
+        <v>75.5</v>
+      </c>
+      <c r="E15" s="110">
+        <f t="shared" si="0"/>
+        <v>111.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="109">
+        <v>12</v>
+      </c>
+      <c r="B16" s="109">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="C16" s="109">
+        <v>30.699999999999996</v>
+      </c>
+      <c r="D16" s="110">
+        <v>83.9</v>
+      </c>
+      <c r="E16" s="110">
+        <f t="shared" si="0"/>
+        <v>114.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="109">
+        <v>13</v>
+      </c>
+      <c r="B17" s="109">
+        <v>2.016</v>
+      </c>
+      <c r="C17" s="109">
+        <v>47.2</v>
+      </c>
+      <c r="D17" s="110">
+        <v>59.5</v>
+      </c>
+      <c r="E17" s="110">
+        <f t="shared" si="0"/>
+        <v>106.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="109">
+        <v>14</v>
+      </c>
+      <c r="B18" s="109">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="C18" s="109">
+        <v>171.3</v>
+      </c>
+      <c r="D18" s="110">
+        <v>188.2</v>
+      </c>
+      <c r="E18" s="110">
+        <f t="shared" si="0"/>
+        <v>359.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="109">
+        <v>15</v>
+      </c>
+      <c r="B19" s="125">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="C19" s="109">
+        <v>29.299999999999997</v>
+      </c>
+      <c r="D19" s="110">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E19" s="110">
+        <f t="shared" si="0"/>
+        <v>48.699999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="109"/>
+      <c r="B20" s="109" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" s="109">
+        <f>SUM(C5:C19)</f>
+        <v>724.40000000000009</v>
+      </c>
+      <c r="D20" s="109">
+        <f t="shared" ref="D20:E20" si="1">SUM(D5:D19)</f>
+        <v>1148.5</v>
+      </c>
+      <c r="E20" s="109">
+        <f t="shared" si="1"/>
+        <v>1872.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="134"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="134"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="132" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="132"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+    </row>
+    <row r="24" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="107"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="107"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="111">
+        <v>1</v>
+      </c>
+      <c r="B26" s="127">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="C26" s="123">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D26" s="123">
+        <v>79.5</v>
+      </c>
+      <c r="E26" s="123">
+        <f>C26+D26</f>
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="111">
+        <v>2</v>
+      </c>
+      <c r="B27" s="111">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="C27" s="123">
+        <v>0</v>
+      </c>
+      <c r="D27" s="123">
+        <v>32.4</v>
+      </c>
+      <c r="E27" s="123">
+        <f t="shared" ref="E27:E30" si="2">C27+D27</f>
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="111">
+        <v>3</v>
+      </c>
+      <c r="B28" s="111">
+        <v>2.0179999999999998</v>
+      </c>
+      <c r="C28" s="123">
+        <v>25.8</v>
+      </c>
+      <c r="D28" s="123">
+        <v>51.9</v>
+      </c>
+      <c r="E28" s="123">
+        <f t="shared" si="2"/>
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="111">
+        <v>4</v>
+      </c>
+      <c r="B29" s="127">
+        <v>2.02</v>
+      </c>
+      <c r="C29" s="123">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D29" s="123">
+        <v>32.4</v>
+      </c>
+      <c r="E29" s="123">
+        <f t="shared" si="2"/>
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="111">
+        <v>5</v>
+      </c>
+      <c r="B30" s="111">
+        <v>2.0209999999999999</v>
+      </c>
+      <c r="C30" s="123">
+        <v>6.9</v>
+      </c>
+      <c r="D30" s="123">
+        <v>25.4</v>
+      </c>
+      <c r="E30" s="123">
+        <f t="shared" si="2"/>
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="111">
+        <v>6</v>
+      </c>
+      <c r="B31" s="111">
+        <v>2.0590000000000002</v>
+      </c>
+      <c r="C31" s="123">
+        <v>7.9</v>
+      </c>
+      <c r="D31" s="123">
+        <v>23.1</v>
+      </c>
+      <c r="E31" s="123">
+        <f>C31+D31</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="111"/>
+      <c r="B32" s="111" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="123">
+        <f>SUM(C25:C30)</f>
+        <v>59</v>
+      </c>
+      <c r="D32" s="123">
+        <f t="shared" ref="D32:E32" si="3">SUM(D25:D30)</f>
+        <v>221.60000000000002</v>
+      </c>
+      <c r="E32" s="123">
+        <f t="shared" si="3"/>
+        <v>280.60000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="K14:L16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="14" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>214</v>
+      </c>
+      <c r="L14" s="124">
+        <f>'2вор'!E3+'3вор1.2с'!E3</f>
+        <v>1766.3400000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>215</v>
+      </c>
+      <c r="L15" s="124">
+        <f>'2вор'!E6+'3вор1.2с'!E6</f>
+        <v>1376.7</v>
+      </c>
+    </row>
+    <row r="16" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="124">
+        <f>'2вор'!E10+'3вор1.2с'!E10</f>
+        <v>2011.5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="29"/>
-    <col min="2" max="2" width="13.7109375" style="29" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="17" style="29" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="108"/>
-    </row>
-    <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
-    </row>
-    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="25">
-        <v>1</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="10">
-        <v>51.28</v>
-      </c>
-      <c r="D5" s="10">
-        <v>29.94</v>
-      </c>
-      <c r="E5" s="12">
-        <f>C5+D5</f>
-        <v>81.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
-        <v>2</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="10">
-        <v>51.69</v>
-      </c>
-      <c r="D6" s="26">
-        <v>50.83</v>
-      </c>
-      <c r="E6" s="12">
-        <f t="shared" ref="E6:E11" si="0">C6+D6</f>
-        <v>102.52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="25">
-        <v>3</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="26">
-        <v>18.690000000000001</v>
-      </c>
-      <c r="D7" s="26">
-        <v>69.78</v>
-      </c>
-      <c r="E7" s="12">
-        <f t="shared" si="0"/>
-        <v>88.47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>4</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="26">
-        <v>72.16</v>
-      </c>
-      <c r="D8" s="26">
-        <v>133.6</v>
-      </c>
-      <c r="E8" s="12">
-        <f t="shared" si="0"/>
-        <v>205.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
-        <v>5</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="26">
-        <v>100.44</v>
-      </c>
-      <c r="D9" s="26">
-        <v>190.18</v>
-      </c>
-      <c r="E9" s="12">
-        <f t="shared" si="0"/>
-        <v>290.62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
-        <v>6</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="26">
-        <v>43.98</v>
-      </c>
-      <c r="D10" s="26">
-        <v>64.37</v>
-      </c>
-      <c r="E10" s="12">
-        <f t="shared" si="0"/>
-        <v>108.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
-        <v>7</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="33">
-        <v>71.78</v>
-      </c>
-      <c r="D11" s="33">
-        <v>64.459999999999994</v>
-      </c>
-      <c r="E11" s="17">
-        <f t="shared" si="0"/>
-        <v>136.24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="20">
-        <f>SUM(C5:C11)</f>
-        <v>410.02</v>
-      </c>
-      <c r="D12" s="20">
-        <f>SUM(D5:D11)</f>
-        <v>603.16000000000008</v>
-      </c>
-      <c r="E12" s="23">
-        <f>SUM(E5:E11)</f>
-        <v>1013.1800000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19432,7 +20832,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="56">
-        <v>233</v>
+        <v>267.16000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -19450,7 +20850,7 @@
       </c>
       <c r="E4" s="56">
         <f>D4*E3</f>
-        <v>23.3</v>
+        <v>26.716000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19468,12 +20868,12 @@
       </c>
       <c r="E5" s="56">
         <f>D5*E3</f>
-        <v>256.3</v>
+        <v>293.87600000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
-        <v>11</v>
+      <c r="A6" s="39">
+        <v>1</v>
       </c>
       <c r="B6" s="40" t="s">
         <v>40</v>
@@ -19485,13 +20885,12 @@
         <v>1</v>
       </c>
       <c r="E6" s="43">
-        <f>'спец 6с'!C13</f>
-        <v>333.82</v>
+        <v>410.02</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>14</v>
+      <c r="A7" s="8">
+        <v>1.1000000000000001</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>8</v>
@@ -19504,12 +20903,12 @@
       </c>
       <c r="E7" s="12">
         <f>$E$6*D7</f>
-        <v>83.454999999999998</v>
+        <v>102.505</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B8" s="38" t="s">
         <v>13</v>
@@ -19521,13 +20920,13 @@
         <v>1.05</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" ref="E8" si="0">$E$6*D8</f>
-        <v>350.51100000000002</v>
+        <f t="shared" ref="E8:E9" si="0">$E$6*D8</f>
+        <v>430.52100000000002</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>18</v>
+      <c r="A9" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>17</v>
@@ -19539,13 +20938,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="19">
-        <f>$E$6*D9*28.57</f>
-        <v>9537.2374</v>
+        <f t="shared" si="0"/>
+        <v>410.02</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="B10" s="40" t="s">
         <v>16</v>
@@ -19557,13 +20956,12 @@
         <v>1</v>
       </c>
       <c r="E10" s="43">
-        <f>'спец 6с'!D13</f>
-        <v>502.91</v>
+        <v>603.16000000000008</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>17</v>
@@ -19575,13 +20973,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="12">
-        <f>$E$10*D11*32.51</f>
-        <v>16349.6041</v>
+        <f>$E$10*D11</f>
+        <v>603.16000000000008</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>10</v>
@@ -19594,12 +20992,12 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
-        <v>75.436499999999995</v>
+        <v>90.474000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>13</v>
@@ -19612,12 +21010,12 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>528.05550000000005</v>
+        <v>633.3180000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>57</v>
+      <c r="A14" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>12</v>
@@ -19629,7 +21027,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="17">
-        <v>97.47</v>
+        <v>295.41000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -19674,7 +21072,7 @@
       </c>
       <c r="E18" s="43">
         <f>E10+E6</f>
-        <v>836.73</v>
+        <v>1013.1800000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -19692,7 +21090,7 @@
       </c>
       <c r="E19" s="19">
         <f>$E$18*D19</f>
-        <v>125.5095</v>
+        <v>151.977</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -19710,7 +21108,7 @@
       </c>
       <c r="E20" s="19">
         <f>$E$18*D20</f>
-        <v>1506.114</v>
+        <v>1823.7240000000002</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19736,7 +21134,1553 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" style="108" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" style="108" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="108" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="108" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="108" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="66"/>
+      <c r="B1" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <f>(E6+E10+E15+E20)*0.45</f>
+        <v>797.26499999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="12">
+        <f>D4*E3</f>
+        <v>79.726500000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="17">
+        <f>D5*E3</f>
+        <v>876.99150000000009</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="63">
+        <v>1</v>
+      </c>
+      <c r="E6" s="64">
+        <f>'3пом'!C16</f>
+        <v>652.29999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>163.07499999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>684.91499999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>18636.210999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'3пом'!D16</f>
+        <v>863</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>28056.129999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>129.44999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>906.15000000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="19">
+        <f>235.75*4</f>
+        <v>943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="118" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="119" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="121">
+        <v>1</v>
+      </c>
+      <c r="E15" s="120">
+        <f>'3пом'!C27</f>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="122" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="121">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="120">
+        <f>D16*$E$15</f>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="121">
+        <v>1</v>
+      </c>
+      <c r="E17" s="120">
+        <f t="shared" ref="E17:E18" si="2">D17*$E$15</f>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="118" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="121">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E18" s="120">
+        <f t="shared" si="2"/>
+        <v>68.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="118" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="121">
+        <v>1.3</v>
+      </c>
+      <c r="E19" s="120">
+        <f>D19*$E$15*40</f>
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="119" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="121">
+        <v>1</v>
+      </c>
+      <c r="E20" s="120">
+        <f>'3пом'!D27</f>
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="122" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="121">
+        <v>0.15</v>
+      </c>
+      <c r="E21" s="120">
+        <f>$E$20*D21</f>
+        <v>29.085000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="118" t="s">
+        <v>208</v>
+      </c>
+      <c r="B22" s="122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="121">
+        <v>1</v>
+      </c>
+      <c r="E22" s="120">
+        <f t="shared" ref="E22:E23" si="3">$E$20*D22</f>
+        <v>193.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="118" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="120" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="121">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E23" s="120">
+        <f t="shared" si="3"/>
+        <v>213.29000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="118" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="122" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="121">
+        <v>1.3</v>
+      </c>
+      <c r="E24" s="120">
+        <f>$E$20*D24*40</f>
+        <v>10082.800000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="114"/>
+      <c r="B26" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="116" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="116" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="113">
+        <v>1</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="11">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10">
+        <f>'3пом'!E16</f>
+        <v>1515.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="113">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E29" s="10">
+        <f>D29*E28</f>
+        <v>227.29499999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" ref="E30:E31" si="4">D30*E29</f>
+        <v>409.13099999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="4"/>
+        <v>122.73929999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" style="108" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="108" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="108" customWidth="1"/>
+    <col min="4" max="4" width="15" style="108" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="108" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="108"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="107"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="107"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="109">
+        <v>1</v>
+      </c>
+      <c r="B5" s="109">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="C5" s="109">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="D5" s="109">
+        <v>55.5</v>
+      </c>
+      <c r="E5" s="109">
+        <v>123.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="109">
+        <v>2</v>
+      </c>
+      <c r="B6" s="109">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="C6" s="109">
+        <v>50.1</v>
+      </c>
+      <c r="D6" s="109">
+        <v>58.2</v>
+      </c>
+      <c r="E6" s="109">
+        <v>108.30000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="109">
+        <v>3</v>
+      </c>
+      <c r="B7" s="109">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="C7" s="109">
+        <v>62.4</v>
+      </c>
+      <c r="D7" s="109">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="E7" s="109">
+        <v>134.30000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="109">
+        <v>4</v>
+      </c>
+      <c r="B8" s="109">
+        <v>3.004</v>
+      </c>
+      <c r="C8" s="109">
+        <v>185.1</v>
+      </c>
+      <c r="D8" s="109">
+        <v>162.9</v>
+      </c>
+      <c r="E8" s="109">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="109">
+        <v>5</v>
+      </c>
+      <c r="B9" s="109">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="C9" s="110">
+        <v>20.8</v>
+      </c>
+      <c r="D9" s="110">
+        <v>11.299999999999999</v>
+      </c>
+      <c r="E9" s="109">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="109">
+        <v>6</v>
+      </c>
+      <c r="B10" s="125">
+        <v>3.01</v>
+      </c>
+      <c r="C10" s="110">
+        <v>38.9</v>
+      </c>
+      <c r="D10" s="110">
+        <v>115.1</v>
+      </c>
+      <c r="E10" s="109">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="109">
+        <v>7</v>
+      </c>
+      <c r="B11" s="109">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="C11" s="110">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="D11" s="110">
+        <v>97.6</v>
+      </c>
+      <c r="E11" s="109">
+        <v>135.30000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="109">
+        <v>8</v>
+      </c>
+      <c r="B12" s="109">
+        <v>3.012</v>
+      </c>
+      <c r="C12" s="110">
+        <v>149.79999999999998</v>
+      </c>
+      <c r="D12" s="110">
+        <v>189.5</v>
+      </c>
+      <c r="E12" s="109">
+        <v>339.29999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="109">
+        <v>9</v>
+      </c>
+      <c r="B13" s="109">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="C13" s="110">
+        <v>30.5</v>
+      </c>
+      <c r="D13" s="110">
+        <v>79.300000000000011</v>
+      </c>
+      <c r="E13" s="109">
+        <v>109.80000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="109">
+        <v>10</v>
+      </c>
+      <c r="B14" s="109">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="C14" s="110">
+        <v>50</v>
+      </c>
+      <c r="D14" s="110">
+        <v>57.7</v>
+      </c>
+      <c r="E14" s="109">
+        <v>107.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="109">
+        <v>11</v>
+      </c>
+      <c r="B15" s="109">
+        <v>3.0670000000000002</v>
+      </c>
+      <c r="C15" s="110">
+        <v>27</v>
+      </c>
+      <c r="D15" s="110">
+        <v>19.5</v>
+      </c>
+      <c r="E15" s="109">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="109"/>
+      <c r="B16" s="109" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="109">
+        <f>SUM(C6:C15)</f>
+        <v>652.29999999999995</v>
+      </c>
+      <c r="D16" s="109">
+        <f t="shared" ref="D16:E16" si="0">SUM(D6:D15)</f>
+        <v>863</v>
+      </c>
+      <c r="E16" s="109">
+        <f t="shared" si="0"/>
+        <v>1515.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+    </row>
+    <row r="19" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="132" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="132"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+    </row>
+    <row r="20" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="107"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="107"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="111">
+        <v>2</v>
+      </c>
+      <c r="B22" s="111">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="C22" s="123">
+        <v>10.1</v>
+      </c>
+      <c r="D22" s="123">
+        <v>77</v>
+      </c>
+      <c r="E22" s="111">
+        <v>87.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="111">
+        <v>3</v>
+      </c>
+      <c r="B23" s="111">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="C23" s="123">
+        <v>21.3</v>
+      </c>
+      <c r="D23" s="123">
+        <v>48.3</v>
+      </c>
+      <c r="E23" s="111">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="111">
+        <v>4</v>
+      </c>
+      <c r="B24" s="111">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="C24" s="123">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D24" s="123">
+        <v>24.700000000000003</v>
+      </c>
+      <c r="E24" s="111">
+        <v>42.800000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="111">
+        <v>5</v>
+      </c>
+      <c r="B25" s="111">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="C25" s="123">
+        <v>7.1</v>
+      </c>
+      <c r="D25" s="123">
+        <v>22.400000000000002</v>
+      </c>
+      <c r="E25" s="111">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="111">
+        <v>6</v>
+      </c>
+      <c r="B26" s="111">
+        <v>3.0289999999999999</v>
+      </c>
+      <c r="C26" s="123">
+        <v>5.9</v>
+      </c>
+      <c r="D26" s="123">
+        <v>21.5</v>
+      </c>
+      <c r="E26" s="111">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="111"/>
+      <c r="B27" s="111" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" s="123">
+        <f>SUM(C21:C26)</f>
+        <v>62.5</v>
+      </c>
+      <c r="D27" s="123">
+        <f t="shared" ref="D27:E27" si="1">SUM(D21:D26)</f>
+        <v>193.9</v>
+      </c>
+      <c r="E27" s="123">
+        <f t="shared" si="1"/>
+        <v>256.39999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="29"/>
+    <col min="2" max="2" width="13.7109375" style="29" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="17" style="29" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="128" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="130"/>
+    </row>
+    <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="131" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="10">
+        <v>51.28</v>
+      </c>
+      <c r="D5" s="10">
+        <v>29.94</v>
+      </c>
+      <c r="E5" s="12">
+        <f>C5+D5</f>
+        <v>81.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>2</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="10">
+        <v>51.69</v>
+      </c>
+      <c r="D6" s="26">
+        <v>50.83</v>
+      </c>
+      <c r="E6" s="12">
+        <f t="shared" ref="E6:E11" si="0">C6+D6</f>
+        <v>102.52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>3</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="26">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="D7" s="26">
+        <v>69.78</v>
+      </c>
+      <c r="E7" s="12">
+        <f t="shared" si="0"/>
+        <v>88.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>4</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="26">
+        <v>72.16</v>
+      </c>
+      <c r="D8" s="26">
+        <v>133.6</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" si="0"/>
+        <v>205.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>5</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="26">
+        <v>100.44</v>
+      </c>
+      <c r="D9" s="26">
+        <v>190.18</v>
+      </c>
+      <c r="E9" s="12">
+        <f t="shared" si="0"/>
+        <v>290.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>6</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="26">
+        <v>43.98</v>
+      </c>
+      <c r="D10" s="26">
+        <v>64.37</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>108.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24">
+        <v>7</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="33">
+        <v>71.78</v>
+      </c>
+      <c r="D11" s="33">
+        <v>64.459999999999994</v>
+      </c>
+      <c r="E11" s="17">
+        <f t="shared" si="0"/>
+        <v>136.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="34"/>
+      <c r="B12" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="20">
+        <f>SUM(C5:C11)</f>
+        <v>410.02</v>
+      </c>
+      <c r="D12" s="20">
+        <f>SUM(D5:D11)</f>
+        <v>603.16000000000008</v>
+      </c>
+      <c r="E12" s="23">
+        <f>SUM(E5:E11)</f>
+        <v>1013.1800000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="57">
+        <v>1</v>
+      </c>
+      <c r="E3" s="56">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="57">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="56">
+        <f>D4*E3</f>
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="57">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="56">
+        <f>D5*E3</f>
+        <v>256.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="42">
+        <v>1</v>
+      </c>
+      <c r="E6" s="43">
+        <f>'спец 6с'!C13</f>
+        <v>333.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E7" s="12">
+        <f>$E$6*D7</f>
+        <v>83.454999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="0">$E$6*D8</f>
+        <v>350.51100000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <f>$E$6*D9*28.57</f>
+        <v>9537.2374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="42">
+        <v>1</v>
+      </c>
+      <c r="E10" s="43">
+        <f>'спец 6с'!D13</f>
+        <v>502.91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12">
+        <f>$E$10*D11*32.51</f>
+        <v>16349.6041</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
+        <v>75.436499999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="E13" s="12">
+        <f t="shared" si="1"/>
+        <v>528.05550000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="16">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>97.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>1</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
+      <c r="E18" s="43">
+        <f>E10+E6</f>
+        <v>836.73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$18*D19</f>
+        <v>125.5095</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="19">
+        <f>$E$18*D20</f>
+        <v>1506.114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>24.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19748,22 +22692,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
@@ -19965,7 +22909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -20323,7 +23267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -20338,22 +23282,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="59"/>
@@ -20464,7 +23408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -20823,7 +23767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -20838,22 +23782,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="132" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="76"/>
@@ -21070,361 +24014,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66"/>
-      <c r="B1" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="72" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="73" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="11">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12">
-        <f>290*3.8</f>
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="12">
-        <f>D4*E3</f>
-        <v>110.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="16">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E5" s="17">
-        <f>D5*E3</f>
-        <v>1212.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="63">
-        <v>1</v>
-      </c>
-      <c r="E6" s="64">
-        <f>Спец7с3э!C16+Спец6с3э!C14+Спец5с3э!C7+Спец4с3э!C16</f>
-        <v>1389.7395421799999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="12">
-        <f>$E$6*D7</f>
-        <v>347.43488554499999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="11">
-        <v>1.05</v>
-      </c>
-      <c r="E8" s="12">
-        <f t="shared" ref="E8" si="0">$E$6*D8</f>
-        <v>1459.226519289</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="13">
-        <v>1</v>
-      </c>
-      <c r="E9" s="19">
-        <f>$E$6*D9*28.57</f>
-        <v>39704.8587200826</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="42">
-        <v>1</v>
-      </c>
-      <c r="E10" s="43">
-        <f>Спец7с3э!D16+Спец6с3э!D14+Спец5с3э!D7+Спец4с3э!D16</f>
-        <v>2747.8019152800002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12">
-        <f>$E$10*D11*32.51</f>
-        <v>89331.040265752803</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="11">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="12">
-        <f t="shared" ref="E12:E13" si="1">$E$10*D12</f>
-        <v>412.17028729200001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1.05</v>
-      </c>
-      <c r="E13" s="12">
-        <f t="shared" si="1"/>
-        <v>2885.1920110440005</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="16">
-        <v>1</v>
-      </c>
-      <c r="E14" s="17">
-        <f>235.75*4</f>
-        <v>943</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="39">
-        <v>1</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="42">
-        <v>1</v>
-      </c>
-      <c r="E18" s="43">
-        <f>E10+E6</f>
-        <v>4137.5414574599999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0.15</v>
-      </c>
-      <c r="E19" s="19">
-        <f>$E$18*D19</f>
-        <v>620.63121861899992</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="11">
-        <v>1.8</v>
-      </c>
-      <c r="E20" s="19">
-        <f>$E$18*D20</f>
-        <v>7447.5746234280005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="22">
-        <v>0.3</v>
-      </c>
-      <c r="E21" s="17">
-        <v>75.13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>